--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -30,84 +30,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>公司</t>
+    <t>条件</t>
   </si>
   <si>
-    <t>源数据excel文件</t>
+    <t>最小值</t>
   </si>
   <si>
-    <t>源数据sheet表格</t>
+    <t>最大值</t>
   </si>
   <si>
-    <t>源数据地址</t>
+    <t>增量比值</t>
   </si>
   <si>
-    <t>目标excel文件</t>
+    <t>增量比值变化率</t>
   </si>
   <si>
-    <t>目标地址</t>
+    <t>计数</t>
   </si>
   <si>
-    <t>招商</t>
+    <t>PPM</t>
   </si>
   <si>
-    <t>全额申报表</t>
-  </si>
-  <si>
-    <t>表1-应税申报表</t>
-  </si>
-  <si>
-    <t>G15</t>
-  </si>
-  <si>
-    <t>上海进化论基金产品应税明细表</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>I15</t>
-  </si>
-  <si>
-    <t>I4</t>
-  </si>
-  <si>
-    <t>F15</t>
-  </si>
-  <si>
-    <t>G5</t>
-  </si>
-  <si>
-    <t>国君</t>
-  </si>
-  <si>
-    <t>STW895</t>
-  </si>
-  <si>
-    <t>营改增税负分析测算明细表</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>G20</t>
-  </si>
-  <si>
-    <t>L12</t>
-  </si>
-  <si>
-    <t>I20</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>G21</t>
-  </si>
-  <si>
-    <t>`</t>
+    <t>方差和平均值</t>
   </si>
 </sst>
 </file>
@@ -273,24 +219,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -611,7 +545,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -635,16 +569,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -653,96 +587,90 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1285,159 +1213,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="17.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="27.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="11.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="32.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2">
+        <v>800</v>
+      </c>
+      <c r="C2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="5:5">
-      <c r="E15" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>条件</t>
   </si>
@@ -41,19 +41,43 @@
     <t>最大值</t>
   </si>
   <si>
-    <t>增量比值</t>
+    <t>UL烟雾-增量比值</t>
   </si>
   <si>
-    <t>增量比值变化率</t>
+    <t>UL烟雾-增量比值变化率</t>
   </si>
   <si>
-    <t>计数</t>
+    <t>UL烟雾-计数</t>
   </si>
   <si>
-    <t>PPM</t>
+    <t>UL烟雾-PPM</t>
   </si>
   <si>
-    <t>方差和平均值</t>
+    <t>UL烟雾-方差和平均值</t>
+  </si>
+  <si>
+    <t>PU烟雾-增量比值</t>
+  </si>
+  <si>
+    <t>PU烟雾-增量比值变化率</t>
+  </si>
+  <si>
+    <t>PU烟雾-计数</t>
+  </si>
+  <si>
+    <t>PU烟雾-PPM</t>
+  </si>
+  <si>
+    <t>PU烟雾-方差和平均值</t>
+  </si>
+  <si>
+    <t>预报警条件(红外)</t>
+  </si>
+  <si>
+    <t>算法启动条件(红外)</t>
+  </si>
+  <si>
+    <t>计数截至条件(红外)</t>
   </si>
 </sst>
 </file>
@@ -219,7 +243,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,6 +252,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -413,12 +455,113 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="18">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -545,7 +688,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -557,120 +700,177 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1213,76 +1413,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="1" max="1" width="23.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>800</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>2000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="7">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="6">
         <v>20</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="9">
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="10">
         <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="12">
+        <v>800</v>
+      </c>
+      <c r="C7" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="15">
+        <v>10</v>
+      </c>
+      <c r="C8" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="15">
+        <v>20</v>
+      </c>
+      <c r="C10" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="18">
+        <v>0</v>
+      </c>
+      <c r="C11" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
   <si>
     <t>条件</t>
   </si>
@@ -1573,9 +1573,158 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="24.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>20</v>
+      </c>
+      <c r="C5" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="12">
+        <v>800</v>
+      </c>
+      <c r="C7" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="15">
+        <v>10</v>
+      </c>
+      <c r="C8" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="15">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="15">
+        <v>20</v>
+      </c>
+      <c r="C10" s="16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="18">
+        <v>0</v>
+      </c>
+      <c r="C11" s="19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>380</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -30,21 +30,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="30">
   <si>
     <t>条件</t>
   </si>
   <si>
+    <t>名称</t>
+  </si>
+  <si>
     <t>最小值</t>
   </si>
   <si>
     <t>最大值</t>
   </si>
   <si>
+    <t>是</t>
+  </si>
+  <si>
     <t>UL烟雾-增量比值</t>
   </si>
   <si>
-    <t>UL烟雾-增量比值变化率</t>
+    <t>UL烟雾-比值变化率</t>
+  </si>
+  <si>
+    <t>×</t>
   </si>
   <si>
     <t>UL烟雾-计数</t>
@@ -59,7 +68,7 @@
     <t>PU烟雾-增量比值</t>
   </si>
   <si>
-    <t>PU烟雾-增量比值变化率</t>
+    <t>PU烟雾-比值变化率</t>
   </si>
   <si>
     <t>PU烟雾-计数</t>
@@ -71,13 +80,46 @@
     <t>PU烟雾-方差和平均值</t>
   </si>
   <si>
-    <t>预报警条件(红外)</t>
-  </si>
-  <si>
-    <t>算法启动条件(红外)</t>
-  </si>
-  <si>
-    <t>计数截至条件(红外)</t>
+    <t>油烟-增量比值</t>
+  </si>
+  <si>
+    <t>油烟-比值变化率</t>
+  </si>
+  <si>
+    <t>油烟-计数</t>
+  </si>
+  <si>
+    <t>油烟-PPM</t>
+  </si>
+  <si>
+    <t>油烟-方差和平均值</t>
+  </si>
+  <si>
+    <t>油烟-结束时红光增量</t>
+  </si>
+  <si>
+    <t>混合烟-数组最大值</t>
+  </si>
+  <si>
+    <t>混合烟-数组最小值</t>
+  </si>
+  <si>
+    <t>混合烟-增量比值范围</t>
+  </si>
+  <si>
+    <t>混合烟-差比值范围</t>
+  </si>
+  <si>
+    <t>通用-A通道的校验差值</t>
+  </si>
+  <si>
+    <t>通用-B通道的校验差值</t>
+  </si>
+  <si>
+    <t>通用-B通道的初始增量</t>
+  </si>
+  <si>
+    <t>通用-灵敏度</t>
   </si>
 </sst>
 </file>
@@ -243,7 +285,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,6 +312,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -455,7 +521,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -479,9 +545,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -505,36 +569,12 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -554,14 +594,71 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -688,7 +785,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -700,55 +797,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -811,14 +896,29 @@
     <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -828,22 +928,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
@@ -855,22 +949,127 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1413,13 +1612,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="23.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
+    <col min="3" max="4" width="7.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1429,142 +1630,300 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="11">
         <v>800</v>
       </c>
-      <c r="C2" s="4">
+      <c r="D7" s="10">
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="13">
         <v>10</v>
       </c>
-      <c r="C3" s="7">
+      <c r="D8" s="12">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6">
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="17">
+        <v>800</v>
+      </c>
+      <c r="D12" s="18">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20">
+        <v>10</v>
+      </c>
+      <c r="D13" s="21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="23">
         <v>0</v>
       </c>
-      <c r="C4" s="7">
+      <c r="D17" s="24">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="27">
+        <v>0</v>
+      </c>
+      <c r="D18" s="28">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="30">
+        <v>200</v>
+      </c>
+      <c r="D19" s="31">
+        <v>65536</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="30">
+        <v>20</v>
+      </c>
+      <c r="D20" s="31">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6">
+    <row r="21" spans="1:4">
+      <c r="A21" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="32">
         <v>20</v>
       </c>
-      <c r="C5" s="7">
+      <c r="D21" s="31">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="9">
-        <v>0</v>
-      </c>
-      <c r="C6" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="12">
-        <v>800</v>
-      </c>
-      <c r="C7" s="13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="15">
-        <v>10</v>
-      </c>
-      <c r="C8" s="16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="15">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="15">
-        <v>20</v>
-      </c>
-      <c r="C10" s="16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="18">
-        <v>0</v>
-      </c>
-      <c r="C11" s="19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>380</v>
-      </c>
+    <row r="22" spans="1:4">
+      <c r="A22" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="53"/>
+      <c r="D22" s="40"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="44"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A25 A2:A11 A12:A16 A18:A19 A20:A21 A22:A24">
+      <formula1>"是,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1573,13 +1932,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="24.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
+    <col min="3" max="4" width="7.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1589,142 +1950,312 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4">
         <v>1000</v>
       </c>
-      <c r="C2" s="4">
+      <c r="D2" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6">
         <v>10</v>
       </c>
-      <c r="C3" s="7">
+      <c r="D3" s="5">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6">
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="11">
+        <v>800</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="13">
+        <v>10</v>
+      </c>
+      <c r="D8" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="14"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="17">
+        <v>800</v>
+      </c>
+      <c r="D12" s="18">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="20">
+        <v>10</v>
+      </c>
+      <c r="D13" s="21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="23">
         <v>0</v>
       </c>
-      <c r="C4" s="7">
+      <c r="D17" s="24">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="27">
+        <v>0</v>
+      </c>
+      <c r="D18" s="28">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="30">
+        <v>200</v>
+      </c>
+      <c r="D19" s="31">
+        <v>65536</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="30">
+        <v>20</v>
+      </c>
+      <c r="D20" s="31">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6">
+    <row r="21" spans="1:4">
+      <c r="A21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="32">
         <v>20</v>
       </c>
-      <c r="C5" s="7">
+      <c r="D21" s="31">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="9">
-        <v>0</v>
-      </c>
-      <c r="C6" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="12">
-        <v>800</v>
-      </c>
-      <c r="C7" s="13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="15">
-        <v>10</v>
-      </c>
-      <c r="C8" s="16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="15">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="15">
-        <v>20</v>
-      </c>
-      <c r="C10" s="16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="18">
-        <v>0</v>
-      </c>
-      <c r="C11" s="19">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>380</v>
-      </c>
+    <row r="22" spans="1:4">
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="37"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="39"/>
+      <c r="D24" s="40"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="48"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A27 A2:A11 A12:A16 A18:A19 A20:A21 A24:A26">
+      <formula1>"是,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="27948" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="32">
   <si>
     <t>条件</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>混合烟-差比值范围</t>
+  </si>
+  <si>
+    <t>通用-算法重置电压</t>
+  </si>
+  <si>
+    <t>通用-计数截至电压</t>
   </si>
   <si>
     <t>通用-A通道的校验差值</t>
@@ -521,7 +527,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -556,8 +562,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -566,6 +576,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -585,8 +606,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -635,30 +660,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -785,7 +786,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -797,34 +798,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -909,7 +910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -928,15 +929,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -949,127 +950,124 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1612,7 +1610,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
@@ -1757,10 +1755,10 @@
       <c r="B12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <v>800</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <v>2000</v>
       </c>
     </row>
@@ -1768,13 +1766,13 @@
       <c r="A13" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <v>10</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <v>60</v>
       </c>
     </row>
@@ -1782,145 +1780,169 @@
       <c r="A14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="21"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="22"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="26">
         <v>0</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="27">
         <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="26" t="s">
+      <c r="A18" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="29">
         <v>0</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="30">
         <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="32">
         <v>200</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="33">
         <v>65536</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="29" t="s">
+      <c r="A20" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="32">
         <v>20</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="33">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="34">
         <v>20</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="33">
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="52" t="s">
+      <c r="A22" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="40"/>
+      <c r="C22" s="37">
+        <v>200</v>
+      </c>
+      <c r="D22" s="38"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="42" t="s">
+      <c r="A23" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="44"/>
+      <c r="C23" s="41">
+        <v>380</v>
+      </c>
+      <c r="D23" s="42"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="46" t="s">
+      <c r="A24" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="48"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="45"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="49" t="s">
+      <c r="A25" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="51"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="47"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A25 A2:A11 A12:A16 A18:A19 A20:A21 A22:A24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A27 A2:A11 A12:A16 A18:A19 A20:A21 A22:A23 A24:A26">
       <formula1>"是,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2077,10 +2099,10 @@
       <c r="B12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <v>800</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <v>2000</v>
       </c>
     </row>
@@ -2088,13 +2110,13 @@
       <c r="A13" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <v>10</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <v>60</v>
       </c>
     </row>
@@ -2102,157 +2124,169 @@
       <c r="A14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="22"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="22"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="21"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="22"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="26">
         <v>0</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="27">
         <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="26" t="s">
+      <c r="A18" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="29">
         <v>0</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="30">
         <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="32">
         <v>200</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="33">
         <v>65536</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="29" t="s">
+      <c r="A20" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="32">
         <v>20</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="33">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="34">
         <v>20</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="33">
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
+      <c r="A22" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="37">
+        <v>200</v>
+      </c>
+      <c r="D22" s="38"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
+      <c r="A23" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="41">
+        <v>380</v>
+      </c>
+      <c r="D23" s="42"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
+      <c r="A24" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="44"/>
+      <c r="D24" s="45"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="44"/>
+      <c r="A25" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="47"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
+      <c r="A26" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
+      <c r="A27" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A27 A2:A11 A12:A16 A18:A19 A20:A21 A24:A26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A27 A2:A11 A12:A16 A18:A19 A20:A21 A22:A23 A24:A26">
       <formula1>"是,×"</formula1>
     </dataValidation>
   </dataValidations>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="35">
   <si>
     <t>条件</t>
   </si>
@@ -44,6 +44,15 @@
     <t>最大值</t>
   </si>
   <si>
+    <t>单点数据</t>
+  </si>
+  <si>
+    <t>×</t>
+  </si>
+  <si>
+    <t>UL烟雾-灵敏度</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
@@ -53,16 +62,16 @@
     <t>UL烟雾-比值变化率</t>
   </si>
   <si>
-    <t>×</t>
-  </si>
-  <si>
     <t>UL烟雾-计数</t>
   </si>
   <si>
     <t>UL烟雾-PPM</t>
   </si>
   <si>
-    <t>UL烟雾-方差和平均值</t>
+    <t>UL烟雾-平均值+方差</t>
+  </si>
+  <si>
+    <t>PU烟雾-灵敏度</t>
   </si>
   <si>
     <t>PU烟雾-增量比值</t>
@@ -77,7 +86,10 @@
     <t>PU烟雾-PPM</t>
   </si>
   <si>
-    <t>PU烟雾-方差和平均值</t>
+    <t>PU烟雾-平均值+方差</t>
+  </si>
+  <si>
+    <t>油烟-灵敏度</t>
   </si>
   <si>
     <t>油烟-增量比值</t>
@@ -92,7 +104,7 @@
     <t>油烟-PPM</t>
   </si>
   <si>
-    <t>油烟-方差和平均值</t>
+    <t>油烟-平均值+方差</t>
   </si>
   <si>
     <t>油烟-结束时红光增量</t>
@@ -110,22 +122,19 @@
     <t>混合烟-差比值范围</t>
   </si>
   <si>
-    <t>通用-算法重置电压</t>
-  </si>
-  <si>
-    <t>通用-计数截至电压</t>
-  </si>
-  <si>
-    <t>通用-A通道的校验差值</t>
-  </si>
-  <si>
-    <t>通用-B通道的校验差值</t>
-  </si>
-  <si>
-    <t>通用-B通道的初始增量</t>
-  </si>
-  <si>
-    <t>通用-灵敏度</t>
+    <t>通用-算法重置电压(B)</t>
+  </si>
+  <si>
+    <t>通用-计数截至电压(A)</t>
+  </si>
+  <si>
+    <t>通用-A通道校机差值</t>
+  </si>
+  <si>
+    <t>通用-B通道校机差值</t>
+  </si>
+  <si>
+    <t>通用-B通道初始增量</t>
   </si>
 </sst>
 </file>
@@ -291,7 +300,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,12 +334,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,39 +554,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -600,33 +570,20 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -639,6 +596,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -646,9 +627,31 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -786,7 +789,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -810,16 +813,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -828,89 +831,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -929,6 +932,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -938,7 +944,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
@@ -947,45 +965,30 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -998,76 +1001,43 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1610,15 +1580,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
     <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
     <col min="3" max="4" width="7.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1631,318 +1601,341 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6">
         <v>1000</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D3" s="7">
+        <v>65535</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="16">
         <v>2000</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="B10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="15">
+        <v>40</v>
+      </c>
+      <c r="D10" s="16">
+        <v>65535</v>
+      </c>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="11">
-        <v>800</v>
-      </c>
-      <c r="D7" s="10">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="13">
-        <v>10</v>
-      </c>
-      <c r="D8" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="12"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="18">
-        <v>800</v>
-      </c>
-      <c r="D12" s="19">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="21">
-        <v>10</v>
-      </c>
-      <c r="D13" s="22">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="22"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="26">
+      <c r="B20" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="26">
         <v>0</v>
       </c>
-      <c r="D17" s="27">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="29">
-        <v>0</v>
-      </c>
-      <c r="D18" s="30">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="32">
+      <c r="D20" s="27">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="27"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36">
         <v>200</v>
       </c>
-      <c r="D19" s="33">
-        <v>65536</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="32">
-        <v>20</v>
-      </c>
-      <c r="D20" s="33">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="34">
-        <v>20</v>
-      </c>
-      <c r="D21" s="33">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="37">
-        <v>200</v>
-      </c>
-      <c r="D22" s="38"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="41">
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39">
         <v>380</v>
       </c>
-      <c r="D23" s="42"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="45"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="49"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="52"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="38"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="38"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A27 A2:A11 A12:A16 A18:A19 A20:A21 A22:A23 A24:A26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1954,15 +1947,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
     <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
     <col min="3" max="4" width="7.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1975,318 +1968,341 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6">
         <v>1000</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D3" s="7">
+        <v>65535</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0</v>
+      </c>
+      <c r="D9" s="16">
         <v>2000</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="B10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="15">
+        <v>40</v>
+      </c>
+      <c r="D10" s="16">
+        <v>65535</v>
+      </c>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="11">
-        <v>800</v>
-      </c>
-      <c r="D7" s="10">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="13">
-        <v>10</v>
-      </c>
-      <c r="D8" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="12"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="14"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="18">
-        <v>800</v>
-      </c>
-      <c r="D12" s="19">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="21">
-        <v>10</v>
-      </c>
-      <c r="D13" s="22">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="22"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="26">
+      <c r="B20" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="26">
         <v>0</v>
       </c>
-      <c r="D17" s="27">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="29">
-        <v>0</v>
-      </c>
-      <c r="D18" s="30">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="32">
+      <c r="D20" s="27">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="27"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="35"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36">
         <v>200</v>
       </c>
-      <c r="D19" s="33">
-        <v>65536</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="32">
-        <v>20</v>
-      </c>
-      <c r="D20" s="33">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="34">
-        <v>20</v>
-      </c>
-      <c r="D21" s="33">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="37">
-        <v>200</v>
-      </c>
-      <c r="D22" s="38"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="41">
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39">
         <v>380</v>
       </c>
-      <c r="D23" s="42"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="44"/>
-      <c r="D24" s="45"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="49"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="52"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="38"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="38"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17 A27 A2:A11 A12:A16 A18:A19 A20:A21 A22:A23 A24:A26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
     </dataValidation>
   </dataValidations>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -1823,10 +1823,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="26">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D20" s="27">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E20" s="27"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="26">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D20" s="27">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E20" s="27"/>
     </row>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -1709,10 +1709,10 @@
         <v>15</v>
       </c>
       <c r="C10" s="15">
-        <v>40</v>
+        <v>-40</v>
       </c>
       <c r="D10" s="16">
-        <v>65535</v>
+        <v>150</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -2076,10 +2076,10 @@
         <v>15</v>
       </c>
       <c r="C10" s="15">
-        <v>40</v>
+        <v>-40</v>
       </c>
       <c r="D10" s="16">
-        <v>65535</v>
+        <v>150</v>
       </c>
       <c r="E10" s="16"/>
     </row>
@@ -2184,7 +2184,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>25</v>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -1991,7 +1991,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="6">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="D3" s="7">
         <v>65535</v>
@@ -2061,7 +2061,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="15">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D9" s="16">
         <v>2000</v>
@@ -2184,16 +2184,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="26">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="27">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="27"/>
     </row>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="35">
   <si>
     <t>条件</t>
   </si>
@@ -913,132 +913,201 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1583,357 +1652,363 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
-    <col min="3" max="4" width="7.66666666666667" customWidth="1"/>
+    <col min="1" max="1" width="5.66666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="4" width="7.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="8">
+        <v>1400</v>
+      </c>
+      <c r="D3" s="9">
+        <v>65535</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9">
+        <v>10</v>
+      </c>
+      <c r="D5" s="9">
+        <v>60</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:5">
+      <c r="A8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:5">
+      <c r="A9" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="20">
+        <v>600</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:5">
+      <c r="A10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="20">
+        <v>-40</v>
+      </c>
+      <c r="D10" s="21">
+        <v>150</v>
+      </c>
+      <c r="E10" s="21"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:5">
+      <c r="A11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:5">
+      <c r="A12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="A13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:5">
+      <c r="A15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:5">
+      <c r="A16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:5">
+      <c r="A17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:5">
+      <c r="A18" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="32">
         <v>1000</v>
       </c>
-      <c r="D3" s="7">
-        <v>65535</v>
-      </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="15">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16">
-        <v>2000</v>
-      </c>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="15">
-        <v>-40</v>
-      </c>
-      <c r="D10" s="16">
-        <v>150</v>
-      </c>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="26">
+      <c r="D20" s="33">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="33"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="44"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45">
         <v>200</v>
       </c>
-      <c r="D20" s="27">
-        <v>600</v>
-      </c>
-      <c r="E20" s="27"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="38" t="s">
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39">
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49">
         <v>380</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="38" t="s">
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="38" t="s">
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="40" t="s">
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:5">
+      <c r="A29" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="6QUpHTLXURaOn2r+2/r4iGBFcpIXwrO1zRWXHeTU7bGLdycw53mDSMkKKWeBKgmy+bJmHtupGLB7INMZ7TRbIg==" saltValue="Wh7bP4SRnqK9SfYvAOUQPw==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
@@ -1950,357 +2025,359 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.66666666666667" customWidth="1"/>
-    <col min="2" max="2" width="23.1111111111111" customWidth="1"/>
-    <col min="3" max="4" width="7.66666666666667" customWidth="1"/>
+    <col min="1" max="1" width="5.66666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="4" width="7.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="8">
         <v>1400</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="9">
         <v>65535</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="3"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="3"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="20">
         <v>600</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="21">
         <v>2000</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="20">
         <v>-40</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="21">
         <v>150</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="21"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="20" t="s">
+      <c r="A14" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="24" t="s">
+      <c r="A19" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="32">
         <v>1000</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="33">
         <v>2000</v>
       </c>
-      <c r="E20" s="27"/>
+      <c r="E20" s="33"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="31" t="s">
+      <c r="A22" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="31" t="s">
+      <c r="A23" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="31" t="s">
+      <c r="A24" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="35" t="s">
+      <c r="A25" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36">
+      <c r="C25" s="44"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45">
         <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="38" t="s">
+      <c r="A26" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39">
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49">
         <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="38" t="s">
+      <c r="A27" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="38" t="s">
+      <c r="A28" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="40" t="s">
+      <c r="A29" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="QF+j3kia1G/YXwCrmdYOwRqSiClMPQnxw77b+QsGfJr4OfiMVJvYwBYUpyXpy0qnNG/H4mxGhFFpvWUT2wlZMg==" saltValue="QuMfom2NC4e6/F90RF+g9Q==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
@@ -2314,9 +2391,367 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.66666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="4" width="7.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="10" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1400</v>
+      </c>
+      <c r="D3" s="9">
+        <v>65535</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:5">
+      <c r="A8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:5">
+      <c r="A9" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="20">
+        <v>600</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:5">
+      <c r="A10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="20">
+        <v>-40</v>
+      </c>
+      <c r="D10" s="21">
+        <v>150</v>
+      </c>
+      <c r="E10" s="21"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:5">
+      <c r="A11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:5">
+      <c r="A12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="A13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:5">
+      <c r="A15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:5">
+      <c r="A16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:5">
+      <c r="A17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:5">
+      <c r="A18" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="32">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="33">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="33"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="44"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:5">
+      <c r="A29" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="hE+QrBDqkud1PVLDSapicYqZmv44r1rNdIzSDIvu3VVz5rX0cJig7NKdG9XSLQqaXpmPk0Kf8/PSocoOlXl39g==" saltValue="KHiZOkLmPD6b+eqs0P8gFQ==" spinCount="100000" sheet="1" objects="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
+      <formula1>"是,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2325,10 +2760,386 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.66666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="4" width="7.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="10" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1400</v>
+      </c>
+      <c r="D3" s="9">
+        <v>65535</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:5">
+      <c r="A8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:5">
+      <c r="A9" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="20">
+        <v>600</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:5">
+      <c r="A10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="20">
+        <v>-40</v>
+      </c>
+      <c r="D10" s="21">
+        <v>150</v>
+      </c>
+      <c r="E10" s="21"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:5">
+      <c r="A11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:5">
+      <c r="A12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="A13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:5">
+      <c r="A15" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:5">
+      <c r="A16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="30"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:5">
+      <c r="A17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:5">
+      <c r="A18" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:5">
+      <c r="A19" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:5">
+      <c r="A20" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="32">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="33">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="33"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:5">
+      <c r="A21" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:5">
+      <c r="A22" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:5">
+      <c r="A23" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="39"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:5">
+      <c r="A24" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:5">
+      <c r="A25" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="44"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:5">
+      <c r="A26" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:5">
+      <c r="A27" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:5">
+      <c r="A28" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:5">
+      <c r="A29" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
+      <formula1>"是,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="1" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="2" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="3" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="4" master="" otherUserPermission="visible"/>
+</allowEditUser>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -1900,7 +1900,7 @@
         <v>1000</v>
       </c>
       <c r="D20" s="33">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E20" s="33"/>
     </row>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -116,10 +116,10 @@
     <t>混合烟-数组最小值</t>
   </si>
   <si>
-    <t>混合烟-增量比值范围</t>
-  </si>
-  <si>
-    <t>混合烟-差比值范围</t>
+    <t>混合烟-增量比值</t>
+  </si>
+  <si>
+    <t>混合烟-比值变化率</t>
   </si>
   <si>
     <t>通用-算法重置电压(B)</t>
@@ -2008,7 +2008,7 @@
       <c r="E29" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6QUpHTLXURaOn2r+2/r4iGBFcpIXwrO1zRWXHeTU7bGLdycw53mDSMkKKWeBKgmy+bJmHtupGLB7INMZ7TRbIg==" saltValue="Wh7bP4SRnqK9SfYvAOUQPw==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="axCKQV/aaE7F8cTkWlZlivfT2TBITBkdV63kKN9/VG3no/gOGK7aM2PcKAACjdunu4kuzpagSMdBQagUc+RdFA==" saltValue="6viemA2HJ5Idacj/XwRlmw==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
@@ -2377,7 +2377,7 @@
       <c r="E29" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QF+j3kia1G/YXwCrmdYOwRqSiClMPQnxw77b+QsGfJr4OfiMVJvYwBYUpyXpy0qnNG/H4mxGhFFpvWUT2wlZMg==" saltValue="QuMfom2NC4e6/F90RF+g9Q==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OGOqTqVQcRXP+5qA1ZgnTXuCTGmB7N4jWUIr40xsH5Barbn4CbL2ISwEdOtcRrqQXbspygb72aXAOSGAufQWaQ==" saltValue="Oyf12KX80B7varKbgXUoqw==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
@@ -2746,7 +2746,7 @@
       <c r="E29" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hE+QrBDqkud1PVLDSapicYqZmv44r1rNdIzSDIvu3VVz5rX0cJig7NKdG9XSLQqaXpmPk0Kf8/PSocoOlXl39g==" saltValue="KHiZOkLmPD6b+eqs0P8gFQ==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6V2rixj9GuPtNSdsOvLc3j+KabbcUmgrMJbZj/an/wlGH98nzQKwbdE7QGmXhjIPrvSbFzPTLPc4lysl7yruLg==" saltValue="ch3PC+6cLy4KoTguEKlWfw==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>
@@ -3115,7 +3115,7 @@
       <c r="E29" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HfjjaHD2NXi9qjhQbwrYtJ5FQqM6sfgVZuleV8+ZCbggUfNKhAKcp70tojXh6p9RMxhBASuYBfULJ6arRJ4l7A==" saltValue="qTG1wp00j8O4/KVfFgzEBw==" spinCount="100000" sheet="1" objects="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A29">
       <formula1>"是,×"</formula1>

--- a/setting/setting.xlsx
+++ b/setting/setting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SC01" sheetId="1" r:id="rId1"/>
@@ -47,16 +47,16 @@
     <t>单点数据</t>
   </si>
   <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>UL烟雾-灵敏度</t>
+  </si>
+  <si>
+    <t>UL烟雾-增量比值</t>
+  </si>
+  <si>
     <t>×</t>
-  </si>
-  <si>
-    <t>UL烟雾-灵敏度</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>UL烟雾-增量比值</t>
   </si>
   <si>
     <t>UL烟雾-比值变化率</t>
@@ -1682,16 +1682,20 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="5">
+        <v>67</v>
+      </c>
+      <c r="D2" s="6">
+        <v>88.9</v>
+      </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="8">
         <v>1400</v>
@@ -1703,7 +1707,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -1714,7 +1718,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>10</v>
@@ -1729,7 +1733,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
@@ -1740,7 +1744,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>12</v>
@@ -1751,7 +1755,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>13</v>
@@ -1762,7 +1766,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:5">
       <c r="A9" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>14</v>
@@ -1777,7 +1781,7 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:5">
       <c r="A10" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>15</v>
@@ -1792,7 +1796,7 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:5">
       <c r="A11" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>16</v>
@@ -1803,7 +1807,7 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:5">
       <c r="A12" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>17</v>
@@ -1814,7 +1818,7 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:5">
       <c r="A13" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>18</v>
@@ -1825,7 +1829,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:5">
       <c r="A14" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>19</v>
@@ -1836,7 +1840,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:5">
       <c r="A15" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>20</v>
@@ -1847,7 +1851,7 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:5">
       <c r="A16" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>21</v>
@@ -1858,7 +1862,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:5">
       <c r="A17" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>22</v>
@@ -1869,7 +1873,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:5">
       <c r="A18" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>23</v>
@@ -1880,7 +1884,7 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:5">
       <c r="A19" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>24</v>
@@ -1891,7 +1895,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:5">
       <c r="A20" s="24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>25</v>
@@ -1906,7 +1910,7 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:5">
       <c r="A21" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>26</v>
@@ -1917,7 +1921,7 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:5">
       <c r="A22" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>27</v>
@@ -1928,7 +1932,7 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:5">
       <c r="A23" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>28</v>
@@ -1939,7 +1943,7 @@
     </row>
     <row r="24" s="1" customFormat="1" spans="1:5">
       <c r="A24" s="36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>29</v>
@@ -1950,7 +1954,7 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="1:5">
       <c r="A25" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>30</v>
@@ -1963,7 +1967,7 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="1:5">
       <c r="A26" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>31</v>
@@ -1976,7 +1980,7 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:5">
       <c r="A27" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>32</v>
@@ -1987,7 +1991,7 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="1:5">
       <c r="A28" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>33</v>
@@ -1998,7 +2002,7 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="1:5">
       <c r="A29" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B29" s="50" t="s">
         <v>34</v>
@@ -2055,16 +2059,20 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="5">
+        <v>66.8</v>
+      </c>
+      <c r="D2" s="6">
+        <v>95.6</v>
+      </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="8">
         <v>1400</v>
@@ -2076,7 +2084,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -2087,7 +2095,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>10</v>
@@ -2098,7 +2106,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
@@ -2109,7 +2117,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>12</v>
@@ -2120,7 +2128,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>13</v>
@@ -2131,7 +2139,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>14</v>
@@ -2146,7 +2154,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>15</v>
@@ -2161,7 +2169,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>16</v>
@@ -2172,7 +2180,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>17</v>
@@ -2183,7 +2191,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>18</v>
@@ -2194,7 +2202,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>19</v>
@@ -2205,7 +2213,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>20</v>
@@ -2216,7 +2224,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>21</v>
@@ -2227,7 +2235,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>22</v>
@@ -2238,7 +2246,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>23</v>
@@ -2249,7 +2257,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>24</v>
@@ -2260,7 +2268,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>25</v>
@@ -2275,7 +2283,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>26</v>
@@ -2286,7 +2294,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>27</v>
@@ -2297,7 +2305,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>28</v>
@@ -2308,7 +2316,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>29</v>
@@ -2319,7 +2327,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>30</v>
@@ -2332,7 +2340,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>31</v>
@@ -2345,7 +2353,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>32</v>
@@ -2356,7 +2364,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>33</v>
@@ -2367,7 +2375,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B29" s="50" t="s">
         <v>34</v>
@@ -2419,7 +2427,7 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>6</v>
@@ -2430,10 +2438,10 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="8">
         <v>1400</v>
@@ -2445,7 +2453,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -2456,7 +2464,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>10</v>
@@ -2467,7 +2475,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
@@ -2478,7 +2486,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>12</v>
@@ -2489,7 +2497,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>13</v>
@@ -2500,7 +2508,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:5">
       <c r="A9" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>14</v>
@@ -2515,7 +2523,7 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:5">
       <c r="A10" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>15</v>
@@ -2530,7 +2538,7 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:5">
       <c r="A11" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>16</v>
@@ -2541,7 +2549,7 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:5">
       <c r="A12" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>17</v>
@@ -2552,7 +2560,7 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:5">
       <c r="A13" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>18</v>
@@ -2563,7 +2571,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:5">
       <c r="A14" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>19</v>
@@ -2574,7 +2582,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:5">
       <c r="A15" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>20</v>
@@ -2585,7 +2593,7 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:5">
       <c r="A16" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>21</v>
@@ -2596,7 +2604,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:5">
       <c r="A17" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>22</v>
@@ -2607,7 +2615,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:5">
       <c r="A18" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>23</v>
@@ -2618,7 +2626,7 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:5">
       <c r="A19" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>24</v>
@@ -2629,7 +2637,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:5">
       <c r="A20" s="24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>25</v>
@@ -2644,7 +2652,7 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:5">
       <c r="A21" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>26</v>
@@ -2655,7 +2663,7 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:5">
       <c r="A22" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>27</v>
@@ -2666,7 +2674,7 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:5">
       <c r="A23" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>28</v>
@@ -2677,7 +2685,7 @@
     </row>
     <row r="24" s="1" customFormat="1" spans="1:5">
       <c r="A24" s="36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>29</v>
@@ -2688,7 +2696,7 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="1:5">
       <c r="A25" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>30</v>
@@ -2701,7 +2709,7 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="1:5">
       <c r="A26" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>31</v>
@@ -2714,7 +2722,7 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:5">
       <c r="A27" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>32</v>
@@ -2725,7 +2733,7 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="1:5">
       <c r="A28" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>33</v>
@@ -2736,7 +2744,7 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="1:5">
       <c r="A29" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B29" s="50" t="s">
         <v>34</v>
@@ -2788,7 +2796,7 @@
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>6</v>
@@ -2799,10 +2807,10 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="8">
         <v>1400</v>
@@ -2814,7 +2822,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>9</v>
@@ -2825,7 +2833,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>10</v>
@@ -2836,7 +2844,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>11</v>
@@ -2847,7 +2855,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>12</v>
@@ -2858,7 +2866,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>13</v>
@@ -2869,7 +2877,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:5">
       <c r="A9" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>14</v>
@@ -2884,7 +2892,7 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:5">
       <c r="A10" s="15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>15</v>
@@ -2899,7 +2907,7 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:5">
       <c r="A11" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>16</v>
@@ -2910,7 +2918,7 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:5">
       <c r="A12" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>17</v>
@@ -2921,7 +2929,7 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:5">
       <c r="A13" s="15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>18</v>
@@ -2932,7 +2940,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:5">
       <c r="A14" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>19</v>
@@ -2943,7 +2951,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:5">
       <c r="A15" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>20</v>
@@ -2954,7 +2962,7 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:5">
       <c r="A16" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>21</v>
@@ -2965,7 +2973,7 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:5">
       <c r="A17" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>22</v>
@@ -2976,7 +2984,7 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:5">
       <c r="A18" s="28" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>23</v>
@@ -2987,7 +2995,7 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:5">
       <c r="A19" s="24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>24</v>
@@ -2998,7 +3006,7 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:5">
       <c r="A20" s="24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>25</v>
@@ -3013,7 +3021,7 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:5">
       <c r="A21" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>26</v>
@@ -3024,7 +3032,7 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:5">
       <c r="A22" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>27</v>
@@ -3035,7 +3043,7 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:5">
       <c r="A23" s="34" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23" s="38" t="s">
         <v>28</v>
@@ -3046,7 +3054,7 @@
     </row>
     <row r="24" s="1" customFormat="1" spans="1:5">
       <c r="A24" s="36" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="38" t="s">
         <v>29</v>
@@ -3057,7 +3065,7 @@
     </row>
     <row r="25" s="1" customFormat="1" spans="1:5">
       <c r="A25" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25" s="43" t="s">
         <v>30</v>
@@ -3070,7 +3078,7 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="1:5">
       <c r="A26" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>31</v>
@@ -3083,7 +3091,7 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:5">
       <c r="A27" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>32</v>
@@ -3094,7 +3102,7 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="1:5">
       <c r="A28" s="46" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>33</v>
@@ -3105,7 +3113,7 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="1:5">
       <c r="A29" s="42" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B29" s="50" t="s">
         <v>34</v>
